--- a/datasets/tenant-inputs/generated/harbortrust-bank/standard-2026-07-v3/core-dimensions/13_evidence_sources.xlsx
+++ b/datasets/tenant-inputs/generated/harbortrust-bank/standard-2026-07-v3/core-dimensions/13_evidence_sources.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="Rf37944a37f9f4c8a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client Intake" sheetId="2" r:id="Ra87f1a89a1744db3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questionnaire" sheetId="3" r:id="R11b72d65604e4ee5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Examples" sheetId="4" r:id="R8c4d205bd88f4d78"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference Values" sheetId="5" r:id="Rfa1c60a01a834d61"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationship Expectations" sheetId="6" r:id="Rbaabfe5463314d42"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="R50b3fa399b5b45d3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client Intake" sheetId="2" r:id="R3dd1c3a6aa9e4d2c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questionnaire" sheetId="3" r:id="R7c46b2b66f29461c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Examples" sheetId="4" r:id="R072cd5447b7e4db0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference Values" sheetId="5" r:id="R8824a48c61a749a7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationship Expectations" sheetId="6" r:id="Rdc44bb2603244297"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -622,7 +622,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R997f8a2cc9e241cd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbbfc58edde7b4164"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -773,7 +773,7 @@
         <x:v>tenant-inputs/generated/harbortrust-bank/standard-2026-07-v3/evidence-manifest/harbortrust-bank-ht-enterprise-ev01.json</x:v>
       </x:c>
       <x:c r="L6" s="78" t="str">
-        <x:v>Client source file, owner attestation, and as-of date must be validated before active use.</x:v>
+        <x:v>Validate HARBORTRUST-BANK-HT-ENTERPRISE-EV01 - Enterprise strategy interview (record 1) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for evidence sources.</x:v>
       </x:c>
       <x:c r="M6" s="41" t="str">
         <x:v>High</x:v>
@@ -814,7 +814,7 @@
         <x:v>tenant-inputs/generated/harbortrust-bank/standard-2026-07-v3/evidence-manifest/harbortrust-bank-ht-enterprise-ev02.json</x:v>
       </x:c>
       <x:c r="L7" s="79" t="str">
-        <x:v>Client source file, owner attestation, and as-of date must be validated before active use.</x:v>
+        <x:v>Confirm HARBORTRUST-BANK-HT-ENTERPRISE-EV02 - FY26 banking priorities workshop (record 2) current-vs-target status, module boundary, volume baseline, and relationship links before this evidence sources record is used downstream.</x:v>
       </x:c>
       <x:c r="M7" s="45" t="str">
         <x:v>High</x:v>
@@ -855,7 +855,7 @@
         <x:v>tenant-inputs/generated/harbortrust-bank/standard-2026-07-v3/evidence-manifest/harbortrust-bank-ht-retail-ev01.json</x:v>
       </x:c>
       <x:c r="L8" t="str">
-        <x:v>Client source file, owner attestation, and as-of date must be validated before active use.</x:v>
+        <x:v>Attach client evidence for HARBORTRUST-BANK-HT-RETAIL-EV01 - Retail banking application inventory (record 3), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="M8" t="str">
         <x:v>High</x:v>
@@ -896,7 +896,7 @@
         <x:v>tenant-inputs/generated/harbortrust-bank/standard-2026-07-v3/evidence-manifest/harbortrust-bank-ht-retail-ev02.json</x:v>
       </x:c>
       <x:c r="L9" t="str">
-        <x:v>Client source file, owner attestation, and as-of date must be validated before active use.</x:v>
+        <x:v>Reconcile HARBORTRUST-BANK-HT-RETAIL-EV02 - Branch operations workshop (record 4) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="M9" t="str">
         <x:v>High</x:v>
@@ -937,7 +937,7 @@
         <x:v>tenant-inputs/generated/harbortrust-bank/standard-2026-07-v3/evidence-manifest/harbortrust-bank-ht-commercial-ev01.json</x:v>
       </x:c>
       <x:c r="L10" t="str">
-        <x:v>Client source file, owner attestation, and as-of date must be validated before active use.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for HARBORTRUST-BANK-HT-COMMERCIAL-EV01 - Commercial LOS export (record 5) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="M10" t="str">
         <x:v>High</x:v>
@@ -978,7 +978,7 @@
         <x:v>tenant-inputs/generated/harbortrust-bank/standard-2026-07-v3/evidence-manifest/harbortrust-bank-ht-commercial-ev02.json</x:v>
       </x:c>
       <x:c r="L11" t="str">
-        <x:v>Client source file, owner attestation, and as-of date must be validated before active use.</x:v>
+        <x:v>Validate HARBORTRUST-BANK-HT-COMMERCIAL-EV02 - Treasury services process map (record 6) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for evidence sources.</x:v>
       </x:c>
       <x:c r="M11" t="str">
         <x:v>High</x:v>
@@ -1019,7 +1019,7 @@
         <x:v>tenant-inputs/generated/harbortrust-bank/standard-2026-07-v3/evidence-manifest/harbortrust-bank-ht-cards-ev01.json</x:v>
       </x:c>
       <x:c r="L12" t="str">
-        <x:v>Client source file, owner attestation, and as-of date must be validated before active use.</x:v>
+        <x:v>Confirm HARBORTRUST-BANK-HT-CARDS-EV01 - Cards platform extract (record 7) current-vs-target status, module boundary, volume baseline, and relationship links before this evidence sources record is used downstream.</x:v>
       </x:c>
       <x:c r="M12" t="str">
         <x:v>High</x:v>
@@ -1060,7 +1060,7 @@
         <x:v>tenant-inputs/generated/harbortrust-bank/standard-2026-07-v3/evidence-manifest/harbortrust-bank-ht-cards-ev02.json</x:v>
       </x:c>
       <x:c r="L13" t="str">
-        <x:v>Client source file, owner attestation, and as-of date must be validated before active use.</x:v>
+        <x:v>Attach client evidence for HARBORTRUST-BANK-HT-CARDS-EV02 - Dispute operations dashboard (record 8), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="M13" t="str">
         <x:v>High</x:v>
@@ -1101,7 +1101,7 @@
         <x:v>tenant-inputs/generated/harbortrust-bank/standard-2026-07-v3/evidence-manifest/harbortrust-bank-ht-payments-ev01.json</x:v>
       </x:c>
       <x:c r="L14" t="str">
-        <x:v>Client source file, owner attestation, and as-of date must be validated before active use.</x:v>
+        <x:v>Reconcile HARBORTRUST-BANK-HT-PAYMENTS-EV01 - Payments hub interface inventory (record 9) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="M14" t="str">
         <x:v>High</x:v>
@@ -1142,7 +1142,7 @@
         <x:v>tenant-inputs/generated/harbortrust-bank/standard-2026-07-v3/evidence-manifest/harbortrust-bank-ht-payments-ev02.json</x:v>
       </x:c>
       <x:c r="L15" t="str">
-        <x:v>Client source file, owner attestation, and as-of date must be validated before active use.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for HARBORTRUST-BANK-HT-PAYMENTS-EV02 - Settlement reconciliation extract (record 10) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="M15" t="str">
         <x:v>High</x:v>
@@ -1183,7 +1183,7 @@
         <x:v>tenant-inputs/generated/harbortrust-bank/standard-2026-07-v3/evidence-manifest/harbortrust-bank-ht-lending-ev01.json</x:v>
       </x:c>
       <x:c r="L16" t="str">
-        <x:v>Client source file, owner attestation, and as-of date must be validated before active use.</x:v>
+        <x:v>Validate HARBORTRUST-BANK-HT-LENDING-EV01 - Loan origination extract (record 11) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for evidence sources.</x:v>
       </x:c>
       <x:c r="M16" t="str">
         <x:v>High</x:v>
@@ -1224,7 +1224,7 @@
         <x:v>tenant-inputs/generated/harbortrust-bank/standard-2026-07-v3/evidence-manifest/harbortrust-bank-ht-lending-ev02.json</x:v>
       </x:c>
       <x:c r="L17" t="str">
-        <x:v>Client source file, owner attestation, and as-of date must be validated before active use.</x:v>
+        <x:v>Confirm HARBORTRUST-BANK-HT-LENDING-EV02 - Underwriting process map (record 12) current-vs-target status, module boundary, volume baseline, and relationship links before this evidence sources record is used downstream.</x:v>
       </x:c>
       <x:c r="M17" t="str">
         <x:v>High</x:v>
@@ -1265,7 +1265,7 @@
         <x:v>tenant-inputs/generated/harbortrust-bank/standard-2026-07-v3/evidence-manifest/harbortrust-bank-ht-wealth-ev01.json</x:v>
       </x:c>
       <x:c r="L18" t="str">
-        <x:v>Client source file, owner attestation, and as-of date must be validated before active use.</x:v>
+        <x:v>Attach client evidence for HARBORTRUST-BANK-HT-WEALTH-EV01 - Wealth platform inventory (record 13), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="M18" t="str">
         <x:v>High</x:v>
@@ -1306,7 +1306,7 @@
         <x:v>tenant-inputs/generated/harbortrust-bank/standard-2026-07-v3/evidence-manifest/harbortrust-bank-ht-wealth-ev02.json</x:v>
       </x:c>
       <x:c r="L19" t="str">
-        <x:v>Client source file, owner attestation, and as-of date must be validated before active use.</x:v>
+        <x:v>Reconcile HARBORTRUST-BANK-HT-WEALTH-EV02 - Advisor reporting catalog (record 14) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="M19" t="str">
         <x:v>High</x:v>
@@ -1347,7 +1347,7 @@
         <x:v>tenant-inputs/generated/harbortrust-bank/standard-2026-07-v3/evidence-manifest/harbortrust-bank-ht-fraud-risk-ev01.json</x:v>
       </x:c>
       <x:c r="L20" t="str">
-        <x:v>Client source file, owner attestation, and as-of date must be validated before active use.</x:v>
+        <x:v>Validate HARBORTRUST-BANK-HT-FRAUD-RISK-EV01 - Fraud alert extract (record 15) against Fraud Analyst Copilot evidence: queue aging mixed with model quality signals; confirm model-risk-approved evaluation set owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="M20" t="str">
         <x:v>High</x:v>
@@ -1388,7 +1388,7 @@
         <x:v>tenant-inputs/generated/harbortrust-bank/standard-2026-07-v3/evidence-manifest/harbortrust-bank-ht-fraud-risk-ev02.json</x:v>
       </x:c>
       <x:c r="L21" t="str">
-        <x:v>Client source file, owner attestation, and as-of date must be validated before active use.</x:v>
+        <x:v>Validate HARBORTRUST-BANK-HT-FRAUD-RISK-EV02 - Risk case workflow sample (record 16) against Fraud Analyst Copilot evidence: case outcome feedback gaps; confirm fraud analyst copilot with cited case packet owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="M21" t="str">
         <x:v>High</x:v>
@@ -1429,7 +1429,7 @@
         <x:v>tenant-inputs/generated/harbortrust-bank/standard-2026-07-v3/evidence-manifest/harbortrust-bank-ht-compliance-ev01.json</x:v>
       </x:c>
       <x:c r="L22" t="str">
-        <x:v>Client source file, owner attestation, and as-of date must be validated before active use.</x:v>
+        <x:v>Confirm HARBORTRUST-BANK-HT-COMPLIANCE-EV01 - Model inventory export (record 17) current-vs-target status, module boundary, volume baseline, and relationship links before this evidence sources record is used downstream.</x:v>
       </x:c>
       <x:c r="M22" t="str">
         <x:v>High</x:v>
@@ -1470,7 +1470,7 @@
         <x:v>tenant-inputs/generated/harbortrust-bank/standard-2026-07-v3/evidence-manifest/harbortrust-bank-ht-compliance-ev02.json</x:v>
       </x:c>
       <x:c r="L23" t="str">
-        <x:v>Client source file, owner attestation, and as-of date must be validated before active use.</x:v>
+        <x:v>Attach client evidence for HARBORTRUST-BANK-HT-COMPLIANCE-EV02 - Regulatory reporting evidence pack (record 18), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="M23" t="str">
         <x:v>High</x:v>
@@ -1511,7 +1511,7 @@
         <x:v>tenant-inputs/generated/harbortrust-bank/standard-2026-07-v3/evidence-manifest/harbortrust-bank-ht-contact-center-ev01.json</x:v>
       </x:c>
       <x:c r="L24" t="str">
-        <x:v>Client source file, owner attestation, and as-of date must be validated before active use.</x:v>
+        <x:v>Reconcile HARBORTRUST-BANK-HT-CONTACT-CENTER-EV01 - Call reason taxonomy (record 19) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="M24" t="str">
         <x:v>High</x:v>
@@ -1552,7 +1552,7 @@
         <x:v>tenant-inputs/generated/harbortrust-bank/standard-2026-07-v3/evidence-manifest/harbortrust-bank-ht-contact-center-ev02.json</x:v>
       </x:c>
       <x:c r="L25" t="str">
-        <x:v>Client source file, owner attestation, and as-of date must be validated before active use.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for HARBORTRUST-BANK-HT-CONTACT-CENTER-EV02 - CRM case extract (record 20) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="M25" t="str">
         <x:v>High</x:v>
@@ -1593,7 +1593,7 @@
         <x:v>tenant-inputs/generated/harbortrust-bank/standard-2026-07-v3/evidence-manifest/harbortrust-bank-ht-digital-onboarding-ev01.json</x:v>
       </x:c>
       <x:c r="L26" t="str">
-        <x:v>Client source file, owner attestation, and as-of date must be validated before active use.</x:v>
+        <x:v>Validate HARBORTRUST-BANK-HT-DIGITAL-ONBOARDING-EV01 - Digital onboarding funnel extract (record 21) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for evidence sources.</x:v>
       </x:c>
       <x:c r="M26" t="str">
         <x:v>High</x:v>
@@ -1634,7 +1634,7 @@
         <x:v>tenant-inputs/generated/harbortrust-bank/standard-2026-07-v3/evidence-manifest/harbortrust-bank-ht-digital-onboarding-ev02.json</x:v>
       </x:c>
       <x:c r="L27" t="str">
-        <x:v>Client source file, owner attestation, and as-of date must be validated before active use.</x:v>
+        <x:v>Confirm HARBORTRUST-BANK-HT-DIGITAL-ONBOARDING-EV02 - KYC vendor report (record 22) current-vs-target status, module boundary, volume baseline, and relationship links before this evidence sources record is used downstream.</x:v>
       </x:c>
       <x:c r="M27" t="str">
         <x:v>High</x:v>
@@ -1675,7 +1675,7 @@
         <x:v>tenant-inputs/generated/harbortrust-bank/standard-2026-07-v3/evidence-manifest/harbortrust-bank-ht-core-modernization-ev01.json</x:v>
       </x:c>
       <x:c r="L28" t="str">
-        <x:v>Client source file, owner attestation, and as-of date must be validated before active use.</x:v>
+        <x:v>Attach client evidence for HARBORTRUST-BANK-HT-CORE-MODERNIZATION-EV01 - Core banking roadmap (record 23), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="M28" t="str">
         <x:v>High</x:v>
@@ -1716,7 +1716,7 @@
         <x:v>tenant-inputs/generated/harbortrust-bank/standard-2026-07-v3/evidence-manifest/harbortrust-bank-ht-core-modernization-ev02.json</x:v>
       </x:c>
       <x:c r="L29" t="str">
-        <x:v>Client source file, owner attestation, and as-of date must be validated before active use.</x:v>
+        <x:v>Reconcile HARBORTRUST-BANK-HT-CORE-MODERNIZATION-EV02 - Mainframe application dependency map (record 24) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="M29" t="str">
         <x:v>High</x:v>
@@ -1757,7 +1757,7 @@
         <x:v>tenant-inputs/generated/harbortrust-bank/standard-2026-07-v3/evidence-manifest/harbortrust-bank-ht-customer-360-ev01.json</x:v>
       </x:c>
       <x:c r="L30" t="str">
-        <x:v>Client source file, owner attestation, and as-of date must be validated before active use.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for HARBORTRUST-BANK-HT-CUSTOMER-360-EV01 - Customer 360 blueprint (record 25) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="M30" t="str">
         <x:v>High</x:v>
@@ -1798,7 +1798,7 @@
         <x:v>tenant-inputs/generated/harbortrust-bank/standard-2026-07-v3/evidence-manifest/harbortrust-bank-ht-customer-360-ev02.json</x:v>
       </x:c>
       <x:c r="L31" t="str">
-        <x:v>Client source file, owner attestation, and as-of date must be validated before active use.</x:v>
+        <x:v>Validate HARBORTRUST-BANK-HT-CUSTOMER-360-EV02 - Identity resolution workshop (record 26) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for evidence sources.</x:v>
       </x:c>
       <x:c r="M31" t="str">
         <x:v>High</x:v>
@@ -1839,7 +1839,7 @@
         <x:v>tenant-inputs/generated/harbortrust-bank/standard-2026-07-v3/evidence-manifest/harbortrust-bank-ht-retail-analytics-ev01.json</x:v>
       </x:c>
       <x:c r="L32" t="str">
-        <x:v>Client source file, owner attestation, and as-of date must be validated before active use.</x:v>
+        <x:v>Confirm HARBORTRUST-BANK-HT-RETAIL-ANALYTICS-EV01 - Retail mart inventory (record 27) current-vs-target status, module boundary, volume baseline, and relationship links before this evidence sources record is used downstream.</x:v>
       </x:c>
       <x:c r="M32" t="str">
         <x:v>High</x:v>
@@ -1880,7 +1880,7 @@
         <x:v>tenant-inputs/generated/harbortrust-bank/standard-2026-07-v3/evidence-manifest/harbortrust-bank-ht-retail-analytics-ev02.json</x:v>
       </x:c>
       <x:c r="L33" t="str">
-        <x:v>Client source file, owner attestation, and as-of date must be validated before active use.</x:v>
+        <x:v>Attach client evidence for HARBORTRUST-BANK-HT-RETAIL-ANALYTICS-EV02 - Branch dashboard catalog (record 28), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="M33" t="str">
         <x:v>High</x:v>
@@ -1921,7 +1921,7 @@
         <x:v>tenant-inputs/generated/harbortrust-bank/standard-2026-07-v3/evidence-manifest/harbortrust-bank-ht-cards-analytics-ev01.json</x:v>
       </x:c>
       <x:c r="L34" t="str">
-        <x:v>Client source file, owner attestation, and as-of date must be validated before active use.</x:v>
+        <x:v>Reconcile HARBORTRUST-BANK-HT-CARDS-ANALYTICS-EV01 - Cards mart inventory (record 29) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="M34" t="str">
         <x:v>High</x:v>
@@ -1962,7 +1962,7 @@
         <x:v>tenant-inputs/generated/harbortrust-bank/standard-2026-07-v3/evidence-manifest/harbortrust-bank-ht-cards-analytics-ev02.json</x:v>
       </x:c>
       <x:c r="L35" t="str">
-        <x:v>Client source file, owner attestation, and as-of date must be validated before active use.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for HARBORTRUST-BANK-HT-CARDS-ANALYTICS-EV02 - Rewards dashboard catalog (record 30) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="M35" t="str">
         <x:v>High</x:v>
@@ -2003,7 +2003,7 @@
         <x:v>tenant-inputs/generated/harbortrust-bank/standard-2026-07-v3/evidence-manifest/harbortrust-bank-ht-payments-analytics-ev01.json</x:v>
       </x:c>
       <x:c r="L36" t="str">
-        <x:v>Client source file, owner attestation, and as-of date must be validated before active use.</x:v>
+        <x:v>Validate HARBORTRUST-BANK-HT-PAYMENTS-ANALYTICS-EV01 - Payments mart inventory (record 31) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for evidence sources.</x:v>
       </x:c>
       <x:c r="M36" t="str">
         <x:v>High</x:v>
@@ -2044,7 +2044,7 @@
         <x:v>tenant-inputs/generated/harbortrust-bank/standard-2026-07-v3/evidence-manifest/harbortrust-bank-ht-payments-analytics-ev02.json</x:v>
       </x:c>
       <x:c r="L37" t="str">
-        <x:v>Client source file, owner attestation, and as-of date must be validated before active use.</x:v>
+        <x:v>Confirm HARBORTRUST-BANK-HT-PAYMENTS-ANALYTICS-EV02 - Settlement dashboard catalog (record 32) current-vs-target status, module boundary, volume baseline, and relationship links before this evidence sources record is used downstream.</x:v>
       </x:c>
       <x:c r="M37" t="str">
         <x:v>High</x:v>
@@ -2085,7 +2085,7 @@
         <x:v>tenant-inputs/generated/harbortrust-bank/standard-2026-07-v3/evidence-manifest/harbortrust-bank-ht-fraud-analytics-ev01.json</x:v>
       </x:c>
       <x:c r="L38" t="str">
-        <x:v>Client source file, owner attestation, and as-of date must be validated before active use.</x:v>
+        <x:v>Validate HARBORTRUST-BANK-HT-FRAUD-ANALYTICS-EV01 - Fraud feature store inventory (record 33) against Fraud Analyst Copilot evidence: queue aging mixed with model quality signals; confirm model-risk-approved evaluation set owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="M38" t="str">
         <x:v>High</x:v>
@@ -2126,7 +2126,7 @@
         <x:v>tenant-inputs/generated/harbortrust-bank/standard-2026-07-v3/evidence-manifest/harbortrust-bank-ht-fraud-analytics-ev02.json</x:v>
       </x:c>
       <x:c r="L39" t="str">
-        <x:v>Client source file, owner attestation, and as-of date must be validated before active use.</x:v>
+        <x:v>Validate HARBORTRUST-BANK-HT-FRAUD-ANALYTICS-EV02 - Case outcome extract (record 34) against Fraud Analyst Copilot evidence: case outcome feedback gaps; confirm fraud analyst copilot with cited case packet owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="M39" t="str">
         <x:v>High</x:v>
@@ -2167,7 +2167,7 @@
         <x:v>tenant-inputs/generated/harbortrust-bank/standard-2026-07-v3/evidence-manifest/harbortrust-bank-ht-data-platform-ev01.json</x:v>
       </x:c>
       <x:c r="L40" t="str">
-        <x:v>Client source file, owner attestation, and as-of date must be validated before active use.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for HARBORTRUST-BANK-HT-DATA-PLATFORM-EV01 - Cloud data platform architecture (record 35) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="M40" t="str">
         <x:v>High</x:v>
@@ -2208,7 +2208,7 @@
         <x:v>tenant-inputs/generated/harbortrust-bank/standard-2026-07-v3/evidence-manifest/harbortrust-bank-ht-data-platform-ev02.json</x:v>
       </x:c>
       <x:c r="L41" t="str">
-        <x:v>Client source file, owner attestation, and as-of date must be validated before active use.</x:v>
+        <x:v>Validate HARBORTRUST-BANK-HT-DATA-PLATFORM-EV02 - Data product certification checklist (record 36) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for evidence sources.</x:v>
       </x:c>
       <x:c r="M41" t="str">
         <x:v>High</x:v>
@@ -2249,7 +2249,7 @@
         <x:v>tenant-inputs/generated/harbortrust-bank/standard-2026-07-v3/evidence-manifest/harbortrust-bank-ht-it-budget-ev01.json</x:v>
       </x:c>
       <x:c r="L42" t="str">
-        <x:v>Client source file, owner attestation, and as-of date must be validated before active use.</x:v>
+        <x:v>Confirm HARBORTRUST-BANK-HT-IT-BUDGET-EV01 - FY26 IT budget export (record 37) current-vs-target status, module boundary, volume baseline, and relationship links before this evidence sources record is used downstream.</x:v>
       </x:c>
       <x:c r="M42" t="str">
         <x:v>High</x:v>
@@ -2290,7 +2290,7 @@
         <x:v>tenant-inputs/generated/harbortrust-bank/standard-2026-07-v3/evidence-manifest/harbortrust-bank-ht-it-budget-ev02.json</x:v>
       </x:c>
       <x:c r="L43" t="str">
-        <x:v>Client source file, owner attestation, and as-of date must be validated before active use.</x:v>
+        <x:v>Attach client evidence for HARBORTRUST-BANK-HT-IT-BUDGET-EV02 - Tower baseline workshop (record 38), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="M43" t="str">
         <x:v>High</x:v>
@@ -2331,7 +2331,7 @@
         <x:v>tenant-inputs/generated/harbortrust-bank/standard-2026-07-v3/evidence-manifest/harbortrust-bank-ht-vendor-sourcing-ev01.json</x:v>
       </x:c>
       <x:c r="L44" t="str">
-        <x:v>Client source file, owner attestation, and as-of date must be validated before active use.</x:v>
+        <x:v>Reconcile HARBORTRUST-BANK-HT-VENDOR-SOURCING-EV01 - Vendor contract extract (record 39) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="M44" t="str">
         <x:v>High</x:v>
@@ -2372,7 +2372,7 @@
         <x:v>tenant-inputs/generated/harbortrust-bank/standard-2026-07-v3/evidence-manifest/harbortrust-bank-ht-vendor-sourcing-ev02.json</x:v>
       </x:c>
       <x:c r="L45" t="str">
-        <x:v>Client source file, owner attestation, and as-of date must be validated before active use.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for HARBORTRUST-BANK-HT-VENDOR-SOURCING-EV02 - AP spend export (record 40) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="M45" t="str">
         <x:v>High</x:v>
@@ -2413,7 +2413,7 @@
         <x:v>tenant-inputs/generated/harbortrust-bank/standard-2026-07-v3/evidence-manifest/harbortrust-bank-ht-cmdb-infra-ev01.json</x:v>
       </x:c>
       <x:c r="L46" t="str">
-        <x:v>Client source file, owner attestation, and as-of date must be validated before active use.</x:v>
+        <x:v>Validate HARBORTRUST-BANK-HT-CMDB-INFRA-EV01 - ServiceNow CMDB export (record 41) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for evidence sources.</x:v>
       </x:c>
       <x:c r="M46" t="str">
         <x:v>High</x:v>
@@ -2454,7 +2454,7 @@
         <x:v>tenant-inputs/generated/harbortrust-bank/standard-2026-07-v3/evidence-manifest/harbortrust-bank-ht-cmdb-infra-ev02.json</x:v>
       </x:c>
       <x:c r="L47" t="str">
-        <x:v>Client source file, owner attestation, and as-of date must be validated before active use.</x:v>
+        <x:v>Confirm HARBORTRUST-BANK-HT-CMDB-INFRA-EV02 - Cloud inventory extract (record 42) current-vs-target status, module boundary, volume baseline, and relationship links before this evidence sources record is used downstream.</x:v>
       </x:c>
       <x:c r="M47" t="str">
         <x:v>High</x:v>
@@ -2495,7 +2495,7 @@
         <x:v>tenant-inputs/generated/harbortrust-bank/standard-2026-07-v3/evidence-manifest/harbortrust-bank-ht-incidents-ev01.json</x:v>
       </x:c>
       <x:c r="L48" t="str">
-        <x:v>Client source file, owner attestation, and as-of date must be validated before active use.</x:v>
+        <x:v>Attach client evidence for HARBORTRUST-BANK-HT-INCIDENTS-EV01 - ServiceNow incident export (record 43), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="M48" t="str">
         <x:v>High</x:v>
@@ -2536,7 +2536,7 @@
         <x:v>tenant-inputs/generated/harbortrust-bank/standard-2026-07-v3/evidence-manifest/harbortrust-bank-ht-incidents-ev02.json</x:v>
       </x:c>
       <x:c r="L49" t="str">
-        <x:v>Client source file, owner attestation, and as-of date must be validated before active use.</x:v>
+        <x:v>Reconcile HARBORTRUST-BANK-HT-INCIDENTS-EV02 - CAB log (record 44) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="M49" t="str">
         <x:v>High</x:v>
@@ -2566,7 +2566,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra8533144700143bb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfcd9feb229cb4b3d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2641,7 +2641,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb5ef43cf19984d59"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R953b38e604ea4570"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2805,7 +2805,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdf95ac515ad44c24"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra4417ff63a5147c7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2891,7 +2891,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R225e92fefc264e60"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7cb0387c8bb240d5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3001,7 +3001,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R80ddb4b01a544ca5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra4fffb3e6fd043f7"/>
   </x:tableParts>
 </x:worksheet>
 </file>